--- a/site/연장근무.xlsx
+++ b/site/연장근무.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김남훈\Desktop\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FBCA9D2-4918-4DD3-8C5F-49A591667956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEC60D2-8F6D-47E1-A723-8668F6427F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1C623E58-0CB5-4E04-92D2-F1145A25538E}"/>
   </bookViews>
   <sheets>
     <sheet name="주 연장근무 현황" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="참고">#REF!</definedName>
     <definedName name="참고2">#REF!</definedName>
@@ -49,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>`</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,10 +97,6 @@
   </si>
   <si>
     <t>박태준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>해외출장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -471,9 +464,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -489,34 +479,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -536,23 +529,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="일일근태"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -845,117 +821,111 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="22"/>
+      <c r="B2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="19"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="J3" s="12" t="s">
         <v>18</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="10">
-        <f>SUM(D4:J4)</f>
-        <v>1.5</v>
+      <c r="C4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="9">
+        <f t="shared" ref="K4:K16" si="0">SUM(D4:J4)</f>
+        <v>0</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="16">
-        <v>6.5</v>
-      </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="10">
-        <f>SUM(D5:J5)</f>
-        <v>6.5</v>
+      <c r="B5" s="21"/>
+      <c r="C5" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="16" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10">
-        <f>SUM(D6:J6)</f>
+      <c r="D6" s="14"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="2"/>
@@ -963,131 +933,119 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="21"/>
+      <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16">
-        <v>2</v>
-      </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="10">
-        <f>SUM(D7:J7)</f>
-        <v>2</v>
+      <c r="D7" s="14"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="18">
-        <v>2</v>
-      </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="10">
-        <f>SUM(D8:J8)</f>
-        <v>2</v>
+      <c r="D8" s="15"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="10">
-        <f>SUM(D9:J9)</f>
-        <v>0.5</v>
+      <c r="D9" s="14"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="16">
-        <v>2</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="10">
-        <f>SUM(D10:J10)</f>
-        <v>2</v>
+      <c r="D10" s="14"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="21"/>
+      <c r="C11" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="16">
-        <v>2</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="10">
-        <f>SUM(D11:J11)</f>
-        <v>2</v>
+      <c r="D11" s="14"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="10">
-        <f>SUM(D12:J12)</f>
+      <c r="D12" s="11"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L12" s="2"/>
@@ -1095,69 +1053,63 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="10">
-        <f>SUM(D13:J13)</f>
-        <v>1.5</v>
+      <c r="D13" s="11"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="10">
-        <f>SUM(D14:J14)</f>
-        <v>1.5</v>
+      <c r="D14" s="11"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="11">
-        <v>0</v>
-      </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="10">
-        <f>SUM(D15:J15)</f>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L15" s="2"/>
@@ -1165,13 +1117,11 @@
     </row>
     <row r="16" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
-      <c r="B16" s="9"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
+      <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1179,7 +1129,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="6"/>
       <c r="K16" s="5">
-        <f>SUM(D16:J16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L16" s="2"/>

--- a/site/연장근무.xlsx
+++ b/site/연장근무.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김남훈\Desktop\site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAFA244-E482-4634-B257-2A20A0423E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D87493-EEC8-4F5F-A940-4AB33F29460C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="135" windowWidth="25290" windowHeight="14565" firstSheet="1" activeTab="1" xr2:uid="{1C623E58-0CB5-4E04-92D2-F1145A25538E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{1C623E58-0CB5-4E04-92D2-F1145A25538E}"/>
   </bookViews>
   <sheets>
     <sheet name="기준" sheetId="3" state="hidden" r:id="rId1"/>
     <sheet name="공휴일" sheetId="6" r:id="rId2"/>
     <sheet name="토요일" sheetId="4" r:id="rId3"/>
     <sheet name="일요일" sheetId="5" r:id="rId4"/>
-    <sheet name="평일" sheetId="2" r:id="rId5"/>
-    <sheet name="주 연장근무 현황" sheetId="1" r:id="rId6"/>
+    <sheet name="월요일" sheetId="7" r:id="rId5"/>
+    <sheet name="평일" sheetId="2" r:id="rId6"/>
+    <sheet name="주 연장근무 현황" sheetId="1" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="참고" localSheetId="0">#REF!</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="79">
   <si>
     <t>`</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -541,7 +542,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1097,6 +1098,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1112,7 +1124,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1338,10 +1350,34 @@
     <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="10" fillId="7" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="10" fillId="7" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1392,7 +1428,7 @@
     <xf numFmtId="176" fontId="10" fillId="7" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,6 +1438,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5249,7 +5294,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -5310,7 +5355,7 @@
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="26">
-        <v>46102</v>
+        <v>46083</v>
       </c>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
@@ -5334,42 +5379,42 @@
     </row>
     <row r="4" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="94" t="s">
+      <c r="G4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
       <c r="N4" s="28">
         <f>B3-1</f>
-        <v>46101</v>
-      </c>
-      <c r="O4" s="79" t="s">
+        <v>46082</v>
+      </c>
+      <c r="O4" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="81"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
       <c r="R4" s="29">
         <f>B3</f>
-        <v>46102</v>
+        <v>46083</v>
       </c>
       <c r="S4" s="30" t="s">
         <v>36</v>
@@ -5381,37 +5426,37 @@
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="84" t="s">
+      <c r="H5" s="91"/>
+      <c r="I5" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="85"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="86" t="s">
+      <c r="J5" s="93"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="88" t="s">
+      <c r="M5" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="86" t="s">
+      <c r="N5" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="90" t="s">
+      <c r="O5" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="92" t="s">
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="77" t="s">
+      <c r="R5" s="85" t="s">
         <v>42</v>
       </c>
       <c r="S5" s="33"/>
@@ -5420,11 +5465,11 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="36" t="s">
         <v>45</v>
       </c>
@@ -5436,17 +5481,17 @@
         <v>45</v>
       </c>
       <c r="K6" s="37"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="87"/>
-      <c r="O6" s="38" t="s">
+      <c r="L6" s="95"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="39" t="s">
+      <c r="P6" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="78"/>
+      <c r="Q6" s="101"/>
+      <c r="R6" s="86"/>
       <c r="S6" s="33"/>
       <c r="U6" s="36" t="s">
         <v>47</v>
@@ -5457,57 +5502,57 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
-      <c r="B7" s="41">
-        <f t="shared" ref="B7:B19" si="0">+ROW()-6</f>
+      <c r="B7" s="77">
+        <f t="shared" ref="B7:B40" si="0">+ROW()-6</f>
         <v>1</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J7" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K7" s="43">
-        <f>IFERROR(VLOOKUP(J7,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I7,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="44">
-        <f>IFERROR(VLOOKUP(K7,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M7" s="45">
-        <f t="shared" ref="M7:M19" si="1">K7</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P7" s="43" t="s">
+      <c r="G7" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H7" s="79"/>
+      <c r="I7" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J7" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K7" s="79">
+        <f>IFERROR(VLOOKUP(J7,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I7,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="78">
+        <f>IFERROR(VLOOKUP(K7,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M7" s="80">
+        <f t="shared" ref="M7:M40" si="1">K7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="81" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P7" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="Q7" s="47">
-        <v>0</v>
-      </c>
-      <c r="R7" s="46" t="s">
+      <c r="Q7" s="79">
+        <v>0</v>
+      </c>
+      <c r="R7" s="81" t="s">
         <v>76</v>
       </c>
       <c r="S7" s="48" t="s">
@@ -5523,55 +5568,55 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
-      <c r="B8" s="50">
+      <c r="B8" s="51">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C8" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="51" t="s">
         <v>57</v>
       </c>
       <c r="F8" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J8" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K8" s="43">
-        <f>IFERROR(VLOOKUP(J8,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I8,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="44">
-        <f>IFERROR(VLOOKUP(K8,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M8" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="54">
-        <v>0</v>
-      </c>
-      <c r="R8" s="46" t="s">
+      <c r="G8" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H8" s="82"/>
+      <c r="I8" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J8" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K8" s="79">
+        <f>IFERROR(VLOOKUP(J8,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I8,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="78">
+        <f>IFERROR(VLOOKUP(K8,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M8" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82">
+        <v>0</v>
+      </c>
+      <c r="R8" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S8" s="48" t="s">
@@ -5587,57 +5632,57 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="17"/>
-      <c r="B9" s="50">
+      <c r="B9" s="51">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H9" s="53"/>
-      <c r="I9" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J9" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K9" s="43">
-        <f>IFERROR(VLOOKUP(J9,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I9,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="44">
-        <f>IFERROR(VLOOKUP(K9,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M9" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P9" s="53" t="s">
+      <c r="G9" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H9" s="82"/>
+      <c r="I9" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J9" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K9" s="79">
+        <f>IFERROR(VLOOKUP(J9,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I9,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="78">
+        <f>IFERROR(VLOOKUP(K9,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M9" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P9" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="Q9" s="54">
-        <v>0</v>
-      </c>
-      <c r="R9" s="46" t="s">
+      <c r="Q9" s="82">
+        <v>0</v>
+      </c>
+      <c r="R9" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S9" s="48" t="s">
@@ -5653,55 +5698,55 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
-      <c r="B10" s="50">
+      <c r="B10" s="51">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H10" s="53"/>
-      <c r="I10" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J10" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K10" s="43">
-        <f>IFERROR(VLOOKUP(J10,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I10,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="44">
-        <f>IFERROR(VLOOKUP(K10,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M10" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="O10" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="54">
-        <v>0</v>
-      </c>
-      <c r="R10" s="46" t="s">
+      <c r="G10" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H10" s="82"/>
+      <c r="I10" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J10" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K10" s="79">
+        <f>IFERROR(VLOOKUP(J10,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I10,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="78">
+        <f>IFERROR(VLOOKUP(K10,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M10" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82">
+        <v>0</v>
+      </c>
+      <c r="R10" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S10" s="48"/>
@@ -5715,57 +5760,57 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
-      <c r="B11" s="50">
+      <c r="B11" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H11" s="55"/>
-      <c r="I11" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J11" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K11" s="43">
-        <f>IFERROR(VLOOKUP(J11,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I11,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="44">
-        <f>IFERROR(VLOOKUP(K11,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M11" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O11" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P11" s="53" t="s">
+      <c r="G11" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H11" s="84"/>
+      <c r="I11" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J11" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K11" s="79">
+        <f>IFERROR(VLOOKUP(J11,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I11,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="78">
+        <f>IFERROR(VLOOKUP(K11,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M11" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P11" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="Q11" s="54">
-        <v>0</v>
-      </c>
-      <c r="R11" s="46" t="s">
+      <c r="Q11" s="82">
+        <v>0</v>
+      </c>
+      <c r="R11" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S11" s="48"/>
@@ -5779,55 +5824,55 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
-      <c r="B12" s="50">
+      <c r="B12" s="51">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H12" s="53"/>
-      <c r="I12" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J12" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K12" s="43">
-        <f>IFERROR(VLOOKUP(J12,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I12,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="44">
-        <f>IFERROR(VLOOKUP(K12,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M12" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O12" s="42">
+      <c r="G12" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H12" s="82"/>
+      <c r="I12" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J12" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K12" s="79">
+        <f>IFERROR(VLOOKUP(J12,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I12,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="78">
+        <f>IFERROR(VLOOKUP(K12,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M12" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="78">
         <v>0.72916666666666696</v>
       </c>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="54">
-        <v>0</v>
-      </c>
-      <c r="R12" s="46" t="s">
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82">
+        <v>0</v>
+      </c>
+      <c r="R12" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S12" s="48"/>
@@ -5841,55 +5886,55 @@
     </row>
     <row r="13" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
-      <c r="B13" s="50">
+      <c r="B13" s="51">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J13" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K13" s="43">
-        <f>IFERROR(VLOOKUP(J13,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I13,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="44">
-        <f>IFERROR(VLOOKUP(K13,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M13" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O13" s="42">
+      <c r="G13" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H13" s="82"/>
+      <c r="I13" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J13" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K13" s="79">
+        <f>IFERROR(VLOOKUP(J13,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I13,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="78">
+        <f>IFERROR(VLOOKUP(K13,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M13" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="78">
         <v>0.72916666666666696</v>
       </c>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="54">
-        <v>0</v>
-      </c>
-      <c r="R13" s="46" t="s">
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82">
+        <v>0</v>
+      </c>
+      <c r="R13" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S13" s="48"/>
@@ -5903,55 +5948,55 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="17"/>
-      <c r="B14" s="50">
+      <c r="B14" s="51">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="G14" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J14" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K14" s="43">
-        <f>IFERROR(VLOOKUP(J14,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I14,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="44">
-        <f>IFERROR(VLOOKUP(K14,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M14" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O14" s="42">
+      <c r="G14" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H14" s="84"/>
+      <c r="I14" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J14" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K14" s="79">
+        <f>IFERROR(VLOOKUP(J14,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I14,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="78">
+        <f>IFERROR(VLOOKUP(K14,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M14" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="78">
         <v>0.72916666666666696</v>
       </c>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="54">
-        <v>0</v>
-      </c>
-      <c r="R14" s="46" t="s">
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82">
+        <v>0</v>
+      </c>
+      <c r="R14" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S14" s="48"/>
@@ -5965,55 +6010,55 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
-      <c r="B15" s="50">
+      <c r="B15" s="51">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C15" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H15" s="55"/>
-      <c r="I15" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J15" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K15" s="43">
-        <f>IFERROR(VLOOKUP(J15,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I15,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="44">
-        <f>IFERROR(VLOOKUP(K15,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M15" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="O15" s="42">
+      <c r="G15" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H15" s="84"/>
+      <c r="I15" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J15" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K15" s="79">
+        <f>IFERROR(VLOOKUP(J15,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I15,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="78">
+        <f>IFERROR(VLOOKUP(K15,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M15" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="78">
         <v>0.72916666666666696</v>
       </c>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="54">
-        <v>0</v>
-      </c>
-      <c r="R15" s="46" t="s">
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82">
+        <v>0</v>
+      </c>
+      <c r="R15" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S15" s="48"/>
@@ -6022,57 +6067,57 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
-      <c r="B16" s="50">
+      <c r="B16" s="51">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C16" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="50" t="s">
+      <c r="D16" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J16" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K16" s="43">
-        <f>IFERROR(VLOOKUP(J16,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I16,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="44">
-        <f>IFERROR(VLOOKUP(K16,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M16" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P16" s="53" t="s">
+      <c r="G16" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H16" s="82"/>
+      <c r="I16" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J16" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K16" s="79">
+        <f>IFERROR(VLOOKUP(J16,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I16,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="78">
+        <f>IFERROR(VLOOKUP(K16,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M16" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P16" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="Q16" s="54">
-        <v>0</v>
-      </c>
-      <c r="R16" s="46" t="s">
+      <c r="Q16" s="82">
+        <v>0</v>
+      </c>
+      <c r="R16" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S16" s="48" t="s">
@@ -6088,57 +6133,57 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="17"/>
-      <c r="B17" s="50">
+      <c r="B17" s="51">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="50" t="s">
+      <c r="D17" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H17" s="55"/>
-      <c r="I17" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J17" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K17" s="43">
-        <f>IFERROR(VLOOKUP(J17,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I17,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="44">
-        <f>IFERROR(VLOOKUP(K17,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M17" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O17" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="P17" s="53" t="s">
+      <c r="G17" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H17" s="84"/>
+      <c r="I17" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J17" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K17" s="79">
+        <f>IFERROR(VLOOKUP(J17,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I17,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="78">
+        <f>IFERROR(VLOOKUP(K17,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M17" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P17" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="Q17" s="54">
-        <v>0</v>
-      </c>
-      <c r="R17" s="46" t="s">
+      <c r="Q17" s="82">
+        <v>0</v>
+      </c>
+      <c r="R17" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S17" s="48" t="s">
@@ -6154,55 +6199,55 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
-      <c r="B18" s="50">
+      <c r="B18" s="51">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C18" s="50" t="s">
+      <c r="C18" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="D18" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="42">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="44">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J18" s="44">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K18" s="43">
-        <f>IFERROR(VLOOKUP(J18,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I18,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="44">
-        <f>IFERROR(VLOOKUP(K18,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M18" s="52">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" s="42">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="P18" s="53"/>
-      <c r="Q18" s="54">
-        <v>0</v>
-      </c>
-      <c r="R18" s="46" t="s">
+      <c r="G18" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H18" s="84"/>
+      <c r="I18" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J18" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K18" s="79">
+        <f>IFERROR(VLOOKUP(J18,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I18,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="78">
+        <f>IFERROR(VLOOKUP(K18,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M18" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="82">
+        <v>0</v>
+      </c>
+      <c r="R18" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S18" s="48"/>
@@ -6216,55 +6261,55 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="17"/>
-      <c r="B19" s="56">
+      <c r="B19" s="51">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="F19" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="57">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="59">
-        <v>0.35416666666666602</v>
-      </c>
-      <c r="J19" s="59">
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="K19" s="60">
-        <f>IFERROR(VLOOKUP(J19,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I19,[1]기준!D:E,2,FALSE),"")</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="59">
-        <f>IFERROR(VLOOKUP(K19,[1]기준!F:G,2,FALSE),"")</f>
-        <v>0.72916666666666663</v>
-      </c>
-      <c r="M19" s="61">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="O19" s="57">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="63">
-        <v>0</v>
-      </c>
-      <c r="R19" s="62" t="s">
+      <c r="G19" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H19" s="82"/>
+      <c r="I19" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J19" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K19" s="79">
+        <f>IFERROR(VLOOKUP(J19,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I19,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="78">
+        <f>IFERROR(VLOOKUP(K19,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M19" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P19" s="82"/>
+      <c r="Q19" s="82">
+        <v>0</v>
+      </c>
+      <c r="R19" s="81" t="s">
         <v>55</v>
       </c>
       <c r="S19" s="48"/>
@@ -6277,6 +6322,57 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="51">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H20" s="82"/>
+      <c r="I20" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K20" s="79">
+        <f>IFERROR(VLOOKUP(J20,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I20,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="78">
+        <f>IFERROR(VLOOKUP(K20,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U20" s="44">
         <v>1</v>
       </c>
@@ -6286,6 +6382,57 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H21" s="82"/>
+      <c r="I21" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K21" s="79">
+        <f>IFERROR(VLOOKUP(J21,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I21,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="78">
+        <f>IFERROR(VLOOKUP(K21,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82">
+        <v>0</v>
+      </c>
+      <c r="R21" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U21" s="44">
         <v>1.0208333333333299</v>
       </c>
@@ -6295,6 +6442,57 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="51">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K22" s="79">
+        <f>IFERROR(VLOOKUP(J22,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I22,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="78">
+        <f>IFERROR(VLOOKUP(K22,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82">
+        <v>0</v>
+      </c>
+      <c r="R22" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U22" s="44">
         <v>1.0416666666666701</v>
       </c>
@@ -6304,6 +6502,57 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="51">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K23" s="79">
+        <f>IFERROR(VLOOKUP(J23,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I23,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78">
+        <f>IFERROR(VLOOKUP(K23,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M23" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82">
+        <v>0</v>
+      </c>
+      <c r="R23" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U23" s="44">
         <v>1.0625</v>
       </c>
@@ -6313,6 +6562,57 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="51">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IFERROR(VLOOKUP(J24,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I24,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="78">
+        <f>IFERROR(VLOOKUP(K24,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M24" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82">
+        <v>0</v>
+      </c>
+      <c r="R24" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U24" s="44">
         <v>1.0833333333333299</v>
       </c>
@@ -6321,8 +6621,866 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="51">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K25" s="79">
+        <f>IFERROR(VLOOKUP(J25,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I25,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="78">
+        <f>IFERROR(VLOOKUP(K25,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M25" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82">
+        <v>0</v>
+      </c>
+      <c r="R25" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="51">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IFERROR(VLOOKUP(J26,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I26,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="78">
+        <f>IFERROR(VLOOKUP(K26,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M26" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82">
+        <v>0</v>
+      </c>
+      <c r="R26" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K27" s="79">
+        <f>IFERROR(VLOOKUP(J27,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I27,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="78">
+        <f>IFERROR(VLOOKUP(K27,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M27" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82">
+        <v>0</v>
+      </c>
+      <c r="R27" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K28" s="79">
+        <f>IFERROR(VLOOKUP(J28,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I28,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="78">
+        <f>IFERROR(VLOOKUP(K28,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M28" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IFERROR(VLOOKUP(J29,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I29,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="78">
+        <f>IFERROR(VLOOKUP(K29,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M29" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K30" s="79">
+        <f>IFERROR(VLOOKUP(J30,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I30,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="78">
+        <f>IFERROR(VLOOKUP(K30,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M30" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82">
+        <v>0</v>
+      </c>
+      <c r="R30" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K31" s="79">
+        <f>IFERROR(VLOOKUP(J31,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I31,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="78">
+        <f>IFERROR(VLOOKUP(K31,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M31" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82">
+        <v>0</v>
+      </c>
+      <c r="R31" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="51">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K32" s="79">
+        <f>IFERROR(VLOOKUP(J32,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I32,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="78">
+        <f>IFERROR(VLOOKUP(K32,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O32" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K33" s="79">
+        <f>IFERROR(VLOOKUP(J33,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I33,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="78">
+        <f>IFERROR(VLOOKUP(K33,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M33" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O33" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="51">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K34" s="79">
+        <f>IFERROR(VLOOKUP(J34,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I34,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="78">
+        <f>IFERROR(VLOOKUP(K34,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O34" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="51">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H35" s="82"/>
+      <c r="I35" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K35" s="79">
+        <f>IFERROR(VLOOKUP(J35,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I35,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="78">
+        <f>IFERROR(VLOOKUP(K35,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M35" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O35" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="51">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K36" s="79">
+        <f>IFERROR(VLOOKUP(J36,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I36,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="78">
+        <f>IFERROR(VLOOKUP(K36,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M36" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82">
+        <v>0</v>
+      </c>
+      <c r="R36" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H37" s="82"/>
+      <c r="I37" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K37" s="79">
+        <f>IFERROR(VLOOKUP(J37,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I37,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="78">
+        <f>IFERROR(VLOOKUP(K37,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M37" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82">
+        <v>0</v>
+      </c>
+      <c r="R37" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K38" s="79">
+        <f>IFERROR(VLOOKUP(J38,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I38,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f>IFERROR(VLOOKUP(K38,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M38" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="51">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H39" s="82"/>
+      <c r="I39" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K39" s="79">
+        <f>IFERROR(VLOOKUP(J39,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I39,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="78">
+        <f>IFERROR(VLOOKUP(K39,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M39" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O39" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="51">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H40" s="82"/>
+      <c r="I40" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K40" s="79">
+        <f>IFERROR(VLOOKUP(J40,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I40,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="78">
+        <f>IFERROR(VLOOKUP(K40,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M40" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="O40" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82">
+        <v>0</v>
+      </c>
+      <c r="R40" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="Q43" t="s">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="G5:H5"/>
@@ -6333,15 +7491,10 @@
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="G4:M4"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O19" xr:uid="{C2F1FDFA-4A63-4E17-9311-8D7CF99AA497}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O40" xr:uid="{C2F1FDFA-4A63-4E17-9311-8D7CF99AA497}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6352,7 +7505,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -6437,39 +7590,39 @@
     </row>
     <row r="4" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="94" t="s">
+      <c r="G4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
       <c r="N4" s="28">
         <f>B3-1</f>
         <v>46101</v>
       </c>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="81"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
       <c r="R4" s="29">
         <f>B3</f>
         <v>46102</v>
@@ -6484,37 +7637,37 @@
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="84" t="s">
+      <c r="H5" s="91"/>
+      <c r="I5" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="85"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="86" t="s">
+      <c r="J5" s="93"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="88" t="s">
+      <c r="M5" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="86" t="s">
+      <c r="N5" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="90" t="s">
+      <c r="O5" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="92" t="s">
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="77" t="s">
+      <c r="R5" s="85" t="s">
         <v>42</v>
       </c>
       <c r="S5" s="33"/>
@@ -6523,11 +7676,11 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="36" t="s">
         <v>45</v>
       </c>
@@ -6539,17 +7692,17 @@
         <v>45</v>
       </c>
       <c r="K6" s="37"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="87"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
       <c r="O6" s="38" t="s">
         <v>45</v>
       </c>
       <c r="P6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="78"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="86"/>
       <c r="S6" s="33"/>
       <c r="U6" s="36" t="s">
         <v>47</v>
@@ -6561,7 +7714,7 @@
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="41">
-        <f t="shared" ref="B7:B19" si="0">+ROW()-6</f>
+        <f t="shared" ref="B7:B43" si="0">+ROW()-6</f>
         <v>1</v>
       </c>
       <c r="C7" s="41" t="s">
@@ -6595,7 +7748,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="M7" s="45">
-        <f t="shared" ref="M7:M19" si="1">K7</f>
+        <f t="shared" ref="M7:M43" si="1">K7</f>
         <v>0</v>
       </c>
       <c r="N7" s="46" t="s">
@@ -7380,6 +8533,59 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="51">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H20" s="84"/>
+      <c r="I20" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K20" s="79">
+        <f>IFERROR(VLOOKUP(J20,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I20,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="78">
+        <f>IFERROR(VLOOKUP(K20,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P20" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U20" s="44">
         <v>1</v>
       </c>
@@ -7389,6 +8595,57 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H21" s="84"/>
+      <c r="I21" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K21" s="79">
+        <f>IFERROR(VLOOKUP(J21,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I21,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="78">
+        <f>IFERROR(VLOOKUP(K21,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82">
+        <v>0</v>
+      </c>
+      <c r="R21" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U21" s="44">
         <v>1.0208333333333299</v>
       </c>
@@ -7398,6 +8655,57 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="51">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K22" s="79">
+        <f>IFERROR(VLOOKUP(J22,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I22,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="78">
+        <f>IFERROR(VLOOKUP(K22,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82">
+        <v>0</v>
+      </c>
+      <c r="R22" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U22" s="44">
         <v>1.0416666666666701</v>
       </c>
@@ -7407,6 +8715,57 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="51">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K23" s="79">
+        <f>IFERROR(VLOOKUP(J23,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I23,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78">
+        <f>IFERROR(VLOOKUP(K23,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M23" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82">
+        <v>0</v>
+      </c>
+      <c r="R23" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U23" s="44">
         <v>1.0625</v>
       </c>
@@ -7416,6 +8775,57 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="51">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IFERROR(VLOOKUP(J24,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I24,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="78">
+        <f>IFERROR(VLOOKUP(K24,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M24" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O24" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82">
+        <v>0</v>
+      </c>
+      <c r="R24" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U24" s="44">
         <v>1.0833333333333299</v>
       </c>
@@ -7424,13 +8834,1015 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="51">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K25" s="79">
+        <f>IFERROR(VLOOKUP(J25,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I25,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="78">
+        <f>IFERROR(VLOOKUP(K25,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M25" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O25" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82">
+        <v>0</v>
+      </c>
+      <c r="R25" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="51">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IFERROR(VLOOKUP(J26,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I26,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="78">
+        <f>IFERROR(VLOOKUP(K26,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M26" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82">
+        <v>0</v>
+      </c>
+      <c r="R26" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K27" s="79">
+        <f>IFERROR(VLOOKUP(J27,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I27,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="78">
+        <f>IFERROR(VLOOKUP(K27,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M27" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82">
+        <v>0</v>
+      </c>
+      <c r="R27" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K28" s="79">
+        <f>IFERROR(VLOOKUP(J28,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I28,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="78">
+        <f>IFERROR(VLOOKUP(K28,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M28" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IFERROR(VLOOKUP(J29,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I29,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="78">
+        <f>IFERROR(VLOOKUP(K29,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M29" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K30" s="79">
+        <f>IFERROR(VLOOKUP(J30,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I30,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="78">
+        <f>IFERROR(VLOOKUP(K30,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M30" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82">
+        <v>0</v>
+      </c>
+      <c r="R30" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K31" s="79">
+        <f>IFERROR(VLOOKUP(J31,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I31,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="78">
+        <f>IFERROR(VLOOKUP(K31,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M31" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O31" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82">
+        <v>0</v>
+      </c>
+      <c r="R31" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="51">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K32" s="79">
+        <f>IFERROR(VLOOKUP(J32,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I32,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="78">
+        <f>IFERROR(VLOOKUP(K32,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O32" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K33" s="79">
+        <f>IFERROR(VLOOKUP(J33,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I33,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="78">
+        <f>IFERROR(VLOOKUP(K33,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M33" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="51">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K34" s="79">
+        <f>IFERROR(VLOOKUP(J34,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I34,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="78">
+        <f>IFERROR(VLOOKUP(K34,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="51">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H35" s="82"/>
+      <c r="I35" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K35" s="79">
+        <f>IFERROR(VLOOKUP(J35,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I35,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="78">
+        <f>IFERROR(VLOOKUP(K35,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M35" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O35" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="51">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K36" s="79">
+        <f>IFERROR(VLOOKUP(J36,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I36,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="78">
+        <f>IFERROR(VLOOKUP(K36,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M36" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O36" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82">
+        <v>0</v>
+      </c>
+      <c r="R36" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H37" s="82"/>
+      <c r="I37" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K37" s="79">
+        <f>IFERROR(VLOOKUP(J37,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I37,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="78">
+        <f>IFERROR(VLOOKUP(K37,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M37" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O37" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82">
+        <v>0</v>
+      </c>
+      <c r="R37" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K38" s="79">
+        <f>IFERROR(VLOOKUP(J38,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I38,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f>IFERROR(VLOOKUP(K38,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M38" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O38" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="51">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H39" s="82"/>
+      <c r="I39" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K39" s="79">
+        <f>IFERROR(VLOOKUP(J39,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I39,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="78">
+        <f>IFERROR(VLOOKUP(K39,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M39" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="51">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H40" s="82"/>
+      <c r="I40" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K40" s="79">
+        <f>IFERROR(VLOOKUP(J40,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I40,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="78">
+        <f>IFERROR(VLOOKUP(K40,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M40" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82">
+        <v>0</v>
+      </c>
+      <c r="R40" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B41" s="51">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H41" s="82"/>
+      <c r="I41" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K41" s="79">
+        <f>IFERROR(VLOOKUP(J41,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I41,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="78">
+        <f>IFERROR(VLOOKUP(K41,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M41" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O41" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82">
+        <v>0</v>
+      </c>
+      <c r="R41" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="51">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K42" s="79">
+        <f>IFERROR(VLOOKUP(J42,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I42,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="78">
+        <f>IFERROR(VLOOKUP(K42,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M42" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O42" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82">
+        <v>0</v>
+      </c>
+      <c r="R42" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="51">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H43" s="82"/>
+      <c r="I43" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K43" s="79">
+        <f>IFERROR(VLOOKUP(J43,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I43,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="78">
+        <f>IFERROR(VLOOKUP(K43,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M43" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O43" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82">
+        <v>0</v>
+      </c>
+      <c r="R43" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="G5:H5"/>
@@ -7441,10 +9853,15 @@
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="G4:M4"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O19" xr:uid="{C8C0AD4C-FB4B-4E06-B50E-582349AC7306}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O43" xr:uid="{C8C0AD4C-FB4B-4E06-B50E-582349AC7306}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7455,7 +9872,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -7540,39 +9957,39 @@
     </row>
     <row r="4" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="94" t="s">
+      <c r="G4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
       <c r="N4" s="28">
         <f>B3-1</f>
         <v>46102</v>
       </c>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="81"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
       <c r="R4" s="29">
         <f>B3</f>
         <v>46103</v>
@@ -7587,37 +10004,37 @@
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="84" t="s">
+      <c r="H5" s="91"/>
+      <c r="I5" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="85"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="86" t="s">
+      <c r="J5" s="93"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="88" t="s">
+      <c r="M5" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="86" t="s">
+      <c r="N5" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="90" t="s">
+      <c r="O5" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="92" t="s">
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="77" t="s">
+      <c r="R5" s="85" t="s">
         <v>42</v>
       </c>
       <c r="S5" s="33"/>
@@ -7626,11 +10043,11 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="36" t="s">
         <v>45</v>
       </c>
@@ -7642,17 +10059,17 @@
         <v>45</v>
       </c>
       <c r="K6" s="37"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="87"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
       <c r="O6" s="38" t="s">
         <v>45</v>
       </c>
       <c r="P6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="78"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="86"/>
       <c r="S6" s="33"/>
       <c r="U6" s="36" t="s">
         <v>47</v>
@@ -7664,7 +10081,7 @@
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="41">
-        <f t="shared" ref="B7:B19" si="0">+ROW()-6</f>
+        <f t="shared" ref="B7:B43" si="0">+ROW()-6</f>
         <v>1</v>
       </c>
       <c r="C7" s="41" t="s">
@@ -7698,7 +10115,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="M7" s="45">
-        <f t="shared" ref="M7:M19" si="1">K7</f>
+        <f t="shared" ref="M7:M43" si="1">K7</f>
         <v>0</v>
       </c>
       <c r="N7" s="46" t="s">
@@ -8460,7 +10877,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="62" t="s">
+      <c r="N19" s="46" t="s">
         <v>55</v>
       </c>
       <c r="O19" s="57">
@@ -8483,6 +10900,59 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="51">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H20" s="84"/>
+      <c r="I20" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K20" s="79">
+        <f>IFERROR(VLOOKUP(J20,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I20,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="78">
+        <f>IFERROR(VLOOKUP(K20,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P20" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U20" s="44">
         <v>1</v>
       </c>
@@ -8492,6 +10962,57 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H21" s="84"/>
+      <c r="I21" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K21" s="79">
+        <f>IFERROR(VLOOKUP(J21,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I21,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="78">
+        <f>IFERROR(VLOOKUP(K21,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82">
+        <v>0</v>
+      </c>
+      <c r="R21" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U21" s="44">
         <v>1.0208333333333299</v>
       </c>
@@ -8501,6 +11022,57 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="51">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K22" s="79">
+        <f>IFERROR(VLOOKUP(J22,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I22,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="78">
+        <f>IFERROR(VLOOKUP(K22,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82">
+        <v>0</v>
+      </c>
+      <c r="R22" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U22" s="44">
         <v>1.0416666666666701</v>
       </c>
@@ -8510,6 +11082,57 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="51">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K23" s="79">
+        <f>IFERROR(VLOOKUP(J23,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I23,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78">
+        <f>IFERROR(VLOOKUP(K23,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M23" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82">
+        <v>0</v>
+      </c>
+      <c r="R23" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U23" s="44">
         <v>1.0625</v>
       </c>
@@ -8519,6 +11142,57 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="51">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IFERROR(VLOOKUP(J24,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I24,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="78">
+        <f>IFERROR(VLOOKUP(K24,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M24" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82">
+        <v>0</v>
+      </c>
+      <c r="R24" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U24" s="44">
         <v>1.0833333333333299</v>
       </c>
@@ -8527,13 +11201,1015 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="51">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K25" s="79">
+        <f>IFERROR(VLOOKUP(J25,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I25,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="78">
+        <f>IFERROR(VLOOKUP(K25,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M25" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82">
+        <v>0</v>
+      </c>
+      <c r="R25" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="51">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IFERROR(VLOOKUP(J26,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I26,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="78">
+        <f>IFERROR(VLOOKUP(K26,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M26" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82">
+        <v>0</v>
+      </c>
+      <c r="R26" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K27" s="79">
+        <f>IFERROR(VLOOKUP(J27,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I27,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="78">
+        <f>IFERROR(VLOOKUP(K27,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M27" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82">
+        <v>0</v>
+      </c>
+      <c r="R27" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K28" s="79">
+        <f>IFERROR(VLOOKUP(J28,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I28,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="78">
+        <f>IFERROR(VLOOKUP(K28,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M28" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IFERROR(VLOOKUP(J29,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I29,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="78">
+        <f>IFERROR(VLOOKUP(K29,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M29" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K30" s="79">
+        <f>IFERROR(VLOOKUP(J30,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I30,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="78">
+        <f>IFERROR(VLOOKUP(K30,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M30" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82">
+        <v>0</v>
+      </c>
+      <c r="R30" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K31" s="79">
+        <f>IFERROR(VLOOKUP(J31,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I31,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="78">
+        <f>IFERROR(VLOOKUP(K31,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M31" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82">
+        <v>0</v>
+      </c>
+      <c r="R31" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="51">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K32" s="79">
+        <f>IFERROR(VLOOKUP(J32,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I32,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="78">
+        <f>IFERROR(VLOOKUP(K32,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O32" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K33" s="79">
+        <f>IFERROR(VLOOKUP(J33,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I33,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="78">
+        <f>IFERROR(VLOOKUP(K33,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M33" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="51">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K34" s="79">
+        <f>IFERROR(VLOOKUP(J34,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I34,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="78">
+        <f>IFERROR(VLOOKUP(K34,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="51">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H35" s="82"/>
+      <c r="I35" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K35" s="79">
+        <f>IFERROR(VLOOKUP(J35,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I35,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="78">
+        <f>IFERROR(VLOOKUP(K35,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M35" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O35" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="51">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K36" s="79">
+        <f>IFERROR(VLOOKUP(J36,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I36,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="78">
+        <f>IFERROR(VLOOKUP(K36,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M36" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82">
+        <v>0</v>
+      </c>
+      <c r="R36" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H37" s="82"/>
+      <c r="I37" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K37" s="79">
+        <f>IFERROR(VLOOKUP(J37,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I37,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="78">
+        <f>IFERROR(VLOOKUP(K37,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M37" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82">
+        <v>0</v>
+      </c>
+      <c r="R37" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K38" s="79">
+        <f>IFERROR(VLOOKUP(J38,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I38,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f>IFERROR(VLOOKUP(K38,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M38" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="51">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H39" s="82"/>
+      <c r="I39" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K39" s="79">
+        <f>IFERROR(VLOOKUP(J39,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I39,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="78">
+        <f>IFERROR(VLOOKUP(K39,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M39" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="51">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H40" s="82"/>
+      <c r="I40" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K40" s="79">
+        <f>IFERROR(VLOOKUP(J40,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I40,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="78">
+        <f>IFERROR(VLOOKUP(K40,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M40" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82">
+        <v>0</v>
+      </c>
+      <c r="R40" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B41" s="51">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H41" s="82"/>
+      <c r="I41" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K41" s="79">
+        <f>IFERROR(VLOOKUP(J41,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I41,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="78">
+        <f>IFERROR(VLOOKUP(K41,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M41" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O41" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82">
+        <v>0</v>
+      </c>
+      <c r="R41" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="51">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K42" s="79">
+        <f>IFERROR(VLOOKUP(J42,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I42,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="78">
+        <f>IFERROR(VLOOKUP(K42,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M42" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O42" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82">
+        <v>0</v>
+      </c>
+      <c r="R42" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="51">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H43" s="82"/>
+      <c r="I43" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K43" s="79">
+        <f>IFERROR(VLOOKUP(J43,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I43,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="78">
+        <f>IFERROR(VLOOKUP(K43,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M43" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O43" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82">
+        <v>0</v>
+      </c>
+      <c r="R43" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="O4:Q4"/>
     <mergeCell ref="G5:H5"/>
@@ -8544,18 +12220,23 @@
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="Q5:Q6"/>
     <mergeCell ref="G4:M4"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O19" xr:uid="{FDE8D584-698D-45FE-B337-8DA2CC088C16}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O43" xr:uid="{FDE8D584-698D-45FE-B337-8DA2CC088C16}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD0A206-2A5D-4A26-964B-3B0A1DF49C06}">
-  <dimension ref="A1:V24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE1B5105-3C65-49AE-A48A-07714573986D}">
+  <dimension ref="A1:V43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
@@ -8640,39 +12321,39 @@
     </row>
     <row r="4" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="75" t="s">
+      <c r="D4" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="75" t="s">
+      <c r="E4" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="75" t="s">
+      <c r="F4" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="94" t="s">
+      <c r="G4" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="96"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
       <c r="N4" s="28">
         <f>B3-1</f>
         <v>46103</v>
       </c>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="81"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
       <c r="R4" s="29">
         <f>B3</f>
         <v>46104</v>
@@ -8687,37 +12368,37 @@
     </row>
     <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="82" t="s">
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="83"/>
-      <c r="I5" s="84" t="s">
+      <c r="H5" s="91"/>
+      <c r="I5" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="85"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="86" t="s">
+      <c r="J5" s="93"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="88" t="s">
+      <c r="M5" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="86" t="s">
+      <c r="N5" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="O5" s="90" t="s">
+      <c r="O5" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="92" t="s">
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="R5" s="77" t="s">
+      <c r="R5" s="85" t="s">
         <v>42</v>
       </c>
       <c r="S5" s="33"/>
@@ -8726,11 +12407,11 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="36" t="s">
         <v>45</v>
       </c>
@@ -8742,17 +12423,17 @@
         <v>45</v>
       </c>
       <c r="K6" s="37"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="87"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
       <c r="O6" s="38" t="s">
         <v>45</v>
       </c>
       <c r="P6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="78"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="86"/>
       <c r="S6" s="33"/>
       <c r="U6" s="36" t="s">
         <v>47</v>
@@ -8764,7 +12445,7 @@
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="41">
-        <f t="shared" ref="B7:B19" si="0">+ROW()-6</f>
+        <f t="shared" ref="B7:B43" si="0">+ROW()-6</f>
         <v>1</v>
       </c>
       <c r="C7" s="41" t="s">
@@ -8812,11 +12493,11 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="M7" s="45">
-        <f t="shared" ref="M7:M19" si="1">K7</f>
+        <f t="shared" ref="M7:M43" si="1">K7</f>
         <v>0</v>
       </c>
       <c r="N7" s="46" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="O7" s="42">
         <v>0.72916666666666663</v>
@@ -8870,7 +12551,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="K8" s="43">
-        <f t="shared" ref="K8:K19" si="2">IF(OR(I8="",J8=""),0,
+        <f t="shared" ref="K8:K18" si="2">IF(OR(I8="",J8=""),0,
 IF(AND(HOUR(I8)=8,MINUTE(I8)=30),
    IF(IF(J8&lt;I8,J8+1,J8)&lt;TIME(18,0,0),0,
       IF(IF(J8&lt;I8,J8+1,J8)&lt;=TIME(19,30,0),
@@ -8896,7 +12577,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O8" s="42">
         <v>0.72916666666666663</v>
@@ -8960,7 +12641,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O9" s="42">
         <v>0.72916666666666663</v>
@@ -9026,7 +12707,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O10" s="42">
         <v>0.72916666666666663</v>
@@ -9088,7 +12769,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O11" s="42">
         <v>0.72916666666666663</v>
@@ -9152,7 +12833,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O12" s="42">
         <v>0.72916666666666696</v>
@@ -9214,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O13" s="42">
         <v>0.72916666666666696</v>
@@ -9276,7 +12957,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O14" s="42">
         <v>0.72916666666666696</v>
@@ -9338,7 +13019,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O15" s="42">
         <v>0.72916666666666696</v>
@@ -9395,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O16" s="42">
         <v>0.72916666666666663</v>
@@ -9461,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O17" s="42">
         <v>0.72916666666666663</v>
@@ -9527,7 +13208,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="46" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O18" s="42">
         <v>0.72916666666666696</v>
@@ -9577,10 +13258,10 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="K19" s="60">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="59">
+        <f>IFERROR(VLOOKUP(J19,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I19,[1]기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="44">
         <f>IFERROR(VLOOKUP(K19,기준!F:G,2,FALSE),"")</f>
         <v>0.72916666666666663</v>
       </c>
@@ -9599,7 +13280,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="62" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S19" s="48"/>
       <c r="U19" s="44">
@@ -9611,6 +13292,59 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="51">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H20" s="84"/>
+      <c r="I20" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K20" s="79">
+        <f>IFERROR(VLOOKUP(J20,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I20,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="78">
+        <f>IFERROR(VLOOKUP(K20,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P20" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U20" s="44">
         <v>1</v>
       </c>
@@ -9620,6 +13354,57 @@
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H21" s="84"/>
+      <c r="I21" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K21" s="79">
+        <f>IFERROR(VLOOKUP(J21,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I21,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="78">
+        <f>IFERROR(VLOOKUP(K21,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82">
+        <v>0</v>
+      </c>
+      <c r="R21" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U21" s="44">
         <v>1.0208333333333299</v>
       </c>
@@ -9629,6 +13414,57 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="51">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K22" s="79">
+        <f>IFERROR(VLOOKUP(J22,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I22,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="78">
+        <f>IFERROR(VLOOKUP(K22,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82">
+        <v>0</v>
+      </c>
+      <c r="R22" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U22" s="44">
         <v>1.0416666666666701</v>
       </c>
@@ -9638,6 +13474,57 @@
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="51">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K23" s="79">
+        <f>IFERROR(VLOOKUP(J23,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I23,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78">
+        <f>IFERROR(VLOOKUP(K23,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M23" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O23" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82">
+        <v>0</v>
+      </c>
+      <c r="R23" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U23" s="44">
         <v>1.0625</v>
       </c>
@@ -9647,12 +13534,1070 @@
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="51">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IFERROR(VLOOKUP(J24,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I24,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="78">
+        <f>IFERROR(VLOOKUP(K24,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M24" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O24" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82">
+        <v>0</v>
+      </c>
+      <c r="R24" s="81" t="s">
+        <v>55</v>
+      </c>
       <c r="U24" s="44">
         <v>1.0833333333333299</v>
       </c>
       <c r="V24" s="64">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="51">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K25" s="79">
+        <f>IFERROR(VLOOKUP(J25,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I25,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="78">
+        <f>IFERROR(VLOOKUP(K25,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M25" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O25" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82">
+        <v>0</v>
+      </c>
+      <c r="R25" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="51">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IFERROR(VLOOKUP(J26,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I26,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="78">
+        <f>IFERROR(VLOOKUP(K26,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M26" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O26" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82">
+        <v>0</v>
+      </c>
+      <c r="R26" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K27" s="79">
+        <f>IFERROR(VLOOKUP(J27,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I27,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="78">
+        <f>IFERROR(VLOOKUP(K27,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M27" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82">
+        <v>0</v>
+      </c>
+      <c r="R27" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K28" s="79">
+        <f>IFERROR(VLOOKUP(J28,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I28,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="78">
+        <f>IFERROR(VLOOKUP(K28,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M28" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IFERROR(VLOOKUP(J29,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I29,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="78">
+        <f>IFERROR(VLOOKUP(K29,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M29" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O29" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K30" s="79">
+        <f>IFERROR(VLOOKUP(J30,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I30,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="78">
+        <f>IFERROR(VLOOKUP(K30,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M30" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O30" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82">
+        <v>0</v>
+      </c>
+      <c r="R30" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K31" s="79">
+        <f>IFERROR(VLOOKUP(J31,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I31,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="78">
+        <f>IFERROR(VLOOKUP(K31,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M31" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O31" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82">
+        <v>0</v>
+      </c>
+      <c r="R31" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="51">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K32" s="79">
+        <f>IFERROR(VLOOKUP(J32,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I32,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="78">
+        <f>IFERROR(VLOOKUP(K32,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O32" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K33" s="79">
+        <f>IFERROR(VLOOKUP(J33,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I33,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="78">
+        <f>IFERROR(VLOOKUP(K33,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M33" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="51">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K34" s="79">
+        <f>IFERROR(VLOOKUP(J34,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I34,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="78">
+        <f>IFERROR(VLOOKUP(K34,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="51">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H35" s="82"/>
+      <c r="I35" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K35" s="79">
+        <f>IFERROR(VLOOKUP(J35,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I35,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="78">
+        <f>IFERROR(VLOOKUP(K35,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M35" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O35" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="51">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K36" s="79">
+        <f>IFERROR(VLOOKUP(J36,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I36,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="78">
+        <f>IFERROR(VLOOKUP(K36,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M36" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O36" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82">
+        <v>0</v>
+      </c>
+      <c r="R36" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H37" s="82"/>
+      <c r="I37" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K37" s="79">
+        <f>IFERROR(VLOOKUP(J37,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I37,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="78">
+        <f>IFERROR(VLOOKUP(K37,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M37" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O37" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82">
+        <v>0</v>
+      </c>
+      <c r="R37" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K38" s="79">
+        <f>IFERROR(VLOOKUP(J38,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I38,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f>IFERROR(VLOOKUP(K38,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M38" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O38" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="51">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H39" s="82"/>
+      <c r="I39" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K39" s="79">
+        <f>IFERROR(VLOOKUP(J39,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I39,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="78">
+        <f>IFERROR(VLOOKUP(K39,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M39" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="51">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H40" s="82"/>
+      <c r="I40" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K40" s="79">
+        <f>IFERROR(VLOOKUP(J40,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I40,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="78">
+        <f>IFERROR(VLOOKUP(K40,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M40" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82">
+        <v>0</v>
+      </c>
+      <c r="R40" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B41" s="51">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H41" s="82"/>
+      <c r="I41" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K41" s="79">
+        <f>IFERROR(VLOOKUP(J41,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I41,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="78">
+        <f>IFERROR(VLOOKUP(K41,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M41" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O41" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82">
+        <v>0</v>
+      </c>
+      <c r="R41" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="51">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K42" s="79">
+        <f>IFERROR(VLOOKUP(J42,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I42,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="78">
+        <f>IFERROR(VLOOKUP(K42,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M42" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O42" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82">
+        <v>0</v>
+      </c>
+      <c r="R42" s="81" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="51">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H43" s="82"/>
+      <c r="I43" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K43" s="79">
+        <f>IFERROR(VLOOKUP(J43,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I43,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="78">
+        <f>IFERROR(VLOOKUP(K43,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M43" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O43" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82">
+        <v>0</v>
+      </c>
+      <c r="R43" s="81" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -9675,13 +14620,2405 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O19" xr:uid="{F8BB5D4A-54AD-4CA4-88F3-ED7FFFEEA735}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O43" xr:uid="{51B93AB5-765E-40E9-8513-6CDC1F5B3B2B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD0A206-2A5D-4A26-964B-3B0A1DF49C06}">
+  <dimension ref="A1:V43"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.625" customWidth="1"/>
+    <col min="2" max="2" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.375" customWidth="1"/>
+    <col min="14" max="14" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8.875" customWidth="1"/>
+    <col min="21" max="21" width="10.375" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="9" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="20"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="25"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="26">
+        <v>46104</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+    </row>
+    <row r="4" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="105" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="105" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="105" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="104"/>
+      <c r="N4" s="28">
+        <f>B3-1</f>
+        <v>46103</v>
+      </c>
+      <c r="O4" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="89"/>
+      <c r="R4" s="29">
+        <f>B3</f>
+        <v>46104</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="32"/>
+    </row>
+    <row r="5" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="91"/>
+      <c r="I5" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="93"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="94" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" s="98" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="100" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" s="33"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="35"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="37"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="P6" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="33"/>
+      <c r="U6" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" s="40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="41">
+        <f t="shared" ref="B7:B43" si="0">+ROW()-6</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H7" s="43"/>
+      <c r="I7" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J7" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K7" s="43">
+        <f>IF(OR(I7="",J7=""),0,
+IF(AND(HOUR(I7)=8,MINUTE(I7)=30),
+   IF(IF(J7&lt;I7,J7+1,J7)&lt;TIME(18,0,0),0,
+      IF(IF(J7&lt;I7,J7+1,J7)&lt;=TIME(19,30,0),
+         ROUND((IF(J7&lt;I7,J7+1,J7)-TIME(17,30,0))*24,1),
+         ROUND((IF(J7&lt;I7,J7+1,J7)-TIME(18,30,0))*24,1)
+      )
+   ),
+   IF(AND(HOUR(I7)=10,MINUTE(I7)=0),
+      IF(IF(J7&lt;I7,J7+1,J7)&lt;=TIME(20,0,0),0,
+         ROUND((IF(J7&lt;I7,J7+1,J7)-TIME(20,0,0))*24,1)
+      ),
+      0
+   )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="44">
+        <f>IFERROR(VLOOKUP(K7,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M7" s="45">
+        <f t="shared" ref="M7:M43" si="1">K7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P7" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q7" s="47">
+        <v>0</v>
+      </c>
+      <c r="R7" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="U7" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="V7" s="49">
+        <f>COUNTIF($I$7:$I$19,U7)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="50">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H8" s="43"/>
+      <c r="I8" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J8" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K8" s="43">
+        <f t="shared" ref="K8:K18" si="2">IF(OR(I8="",J8=""),0,
+IF(AND(HOUR(I8)=8,MINUTE(I8)=30),
+   IF(IF(J8&lt;I8,J8+1,J8)&lt;TIME(18,0,0),0,
+      IF(IF(J8&lt;I8,J8+1,J8)&lt;=TIME(19,30,0),
+         ROUND((IF(J8&lt;I8,J8+1,J8)-TIME(17,30,0))*24,1),
+         ROUND((IF(J8&lt;I8,J8+1,J8)-TIME(18,30,0))*24,1)
+      )
+   ),
+   IF(AND(HOUR(I8)=10,MINUTE(I8)=0),
+      IF(IF(J8&lt;I8,J8+1,J8)&lt;=TIME(20,0,0),0,
+         ROUND((IF(J8&lt;I8,J8+1,J8)-TIME(20,0,0))*24,1)
+      ),
+      0
+   )
+))</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="44">
+        <f>IFERROR(VLOOKUP(K8,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M8" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P8" s="53"/>
+      <c r="Q8" s="54">
+        <v>0</v>
+      </c>
+      <c r="R8" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="U8" s="44">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="V8" s="49">
+        <f>COUNTIF($I$7:$I$19,U8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="50">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H9" s="53"/>
+      <c r="I9" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J9" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K9" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="44">
+        <f>IFERROR(VLOOKUP(K9,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M9" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P9" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="54">
+        <v>0</v>
+      </c>
+      <c r="R9" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S9" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="U9" s="44">
+        <v>0.41666666666666602</v>
+      </c>
+      <c r="V9" s="49">
+        <f>COUNTIF($I$7:$I$19,U9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="50">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H10" s="53"/>
+      <c r="I10" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J10" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K10" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="44">
+        <f>IFERROR(VLOOKUP(K10,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M10" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="54">
+        <v>0</v>
+      </c>
+      <c r="R10" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10" s="48"/>
+      <c r="U10" s="44">
+        <v>0.5625</v>
+      </c>
+      <c r="V10" s="49">
+        <f>COUNTIF($I$7:$I$19,U10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="50">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H11" s="55"/>
+      <c r="I11" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J11" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K11" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="44">
+        <f>IFERROR(VLOOKUP(K11,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M11" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O11" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P11" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="54">
+        <v>0</v>
+      </c>
+      <c r="R11" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S11" s="48"/>
+      <c r="U11" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="V11" s="49">
+        <f t="shared" ref="V11:V24" si="3">COUNTIF($J$7:$J$19,U11)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="50">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H12" s="53"/>
+      <c r="I12" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J12" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K12" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="44">
+        <f>IFERROR(VLOOKUP(K12,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M12" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="42">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="54">
+        <v>0</v>
+      </c>
+      <c r="R12" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S12" s="48"/>
+      <c r="U12" s="44">
+        <v>0.75</v>
+      </c>
+      <c r="V12" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="50">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H13" s="53"/>
+      <c r="I13" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J13" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K13" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="44">
+        <f>IFERROR(VLOOKUP(K13,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M13" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="42">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="54">
+        <v>0</v>
+      </c>
+      <c r="R13" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S13" s="48"/>
+      <c r="U13" s="44">
+        <v>0.77083333333333304</v>
+      </c>
+      <c r="V13" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="50">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H14" s="55"/>
+      <c r="I14" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J14" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K14" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="44">
+        <f>IFERROR(VLOOKUP(K14,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M14" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="42">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P14" s="53"/>
+      <c r="Q14" s="54">
+        <v>0</v>
+      </c>
+      <c r="R14" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S14" s="48"/>
+      <c r="U14" s="44">
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="V14" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="50">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H15" s="55"/>
+      <c r="I15" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J15" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K15" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="44">
+        <f>IFERROR(VLOOKUP(K15,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M15" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="42">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P15" s="53"/>
+      <c r="Q15" s="54">
+        <v>0</v>
+      </c>
+      <c r="R15" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S15" s="48"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="49"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="50">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H16" s="53"/>
+      <c r="I16" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J16" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K16" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="44">
+        <f>IFERROR(VLOOKUP(K16,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M16" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P16" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q16" s="54">
+        <v>0</v>
+      </c>
+      <c r="R16" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S16" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="U16" s="44">
+        <v>0.8125</v>
+      </c>
+      <c r="V16" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+      <c r="B17" s="50">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H17" s="55"/>
+      <c r="I17" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J17" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K17" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="44">
+        <f>IFERROR(VLOOKUP(K17,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M17" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P17" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="54">
+        <v>0</v>
+      </c>
+      <c r="R17" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S17" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="U17" s="42">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V17" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="50">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C18" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="42">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H18" s="55"/>
+      <c r="I18" s="44">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J18" s="44">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K18" s="43">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="44">
+        <f>IFERROR(VLOOKUP(K18,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M18" s="52">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" s="42">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P18" s="53"/>
+      <c r="Q18" s="54">
+        <v>0</v>
+      </c>
+      <c r="R18" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S18" s="48"/>
+      <c r="U18" s="44">
+        <v>0.875000000000001</v>
+      </c>
+      <c r="V18" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="56">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="57">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H19" s="58"/>
+      <c r="I19" s="59">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J19" s="59">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K19" s="60">
+        <f>IFERROR(VLOOKUP(J19,[1]기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I19,[1]기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="44">
+        <f>IFERROR(VLOOKUP(K19,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M19" s="61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="57">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="63">
+        <v>0</v>
+      </c>
+      <c r="R19" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="S19" s="48"/>
+      <c r="U19" s="44">
+        <v>0.89583333333333404</v>
+      </c>
+      <c r="V19" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="51">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C20" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H20" s="84"/>
+      <c r="I20" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K20" s="79">
+        <f>IFERROR(VLOOKUP(J20,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I20,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="78">
+        <f>IFERROR(VLOOKUP(K20,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M20" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O20" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P20" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q20" s="82">
+        <v>0</v>
+      </c>
+      <c r="R20" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="U20" s="44">
+        <v>1</v>
+      </c>
+      <c r="V20" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="51">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H21" s="84"/>
+      <c r="I21" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K21" s="79">
+        <f>IFERROR(VLOOKUP(J21,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I21,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="78">
+        <f>IFERROR(VLOOKUP(K21,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M21" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O21" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P21" s="82"/>
+      <c r="Q21" s="82">
+        <v>0</v>
+      </c>
+      <c r="R21" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="U21" s="44">
+        <v>1.0208333333333299</v>
+      </c>
+      <c r="V21" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="51">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H22" s="82"/>
+      <c r="I22" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K22" s="79">
+        <f>IFERROR(VLOOKUP(J22,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I22,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="78">
+        <f>IFERROR(VLOOKUP(K22,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M22" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O22" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P22" s="82"/>
+      <c r="Q22" s="82">
+        <v>0</v>
+      </c>
+      <c r="R22" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="U22" s="44">
+        <v>1.0416666666666701</v>
+      </c>
+      <c r="V22" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="51">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H23" s="82"/>
+      <c r="I23" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J23" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K23" s="79">
+        <f>IFERROR(VLOOKUP(J23,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I23,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78">
+        <f>IFERROR(VLOOKUP(K23,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M23" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N23" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82">
+        <v>0</v>
+      </c>
+      <c r="R23" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="U23" s="44">
+        <v>1.0625</v>
+      </c>
+      <c r="V23" s="49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="51">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J24" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K24" s="79">
+        <f>IFERROR(VLOOKUP(J24,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I24,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="78">
+        <f>IFERROR(VLOOKUP(K24,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M24" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P24" s="82"/>
+      <c r="Q24" s="82">
+        <v>0</v>
+      </c>
+      <c r="R24" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="U24" s="44">
+        <v>1.0833333333333299</v>
+      </c>
+      <c r="V24" s="64">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="51">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H25" s="82"/>
+      <c r="I25" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J25" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K25" s="79">
+        <f>IFERROR(VLOOKUP(J25,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I25,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="78">
+        <f>IFERROR(VLOOKUP(K25,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M25" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O25" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P25" s="82"/>
+      <c r="Q25" s="82">
+        <v>0</v>
+      </c>
+      <c r="R25" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="51">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H26" s="82"/>
+      <c r="I26" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J26" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K26" s="79">
+        <f>IFERROR(VLOOKUP(J26,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I26,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="78">
+        <f>IFERROR(VLOOKUP(K26,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M26" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O26" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P26" s="82"/>
+      <c r="Q26" s="82">
+        <v>0</v>
+      </c>
+      <c r="R26" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="51">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H27" s="82"/>
+      <c r="I27" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K27" s="79">
+        <f>IFERROR(VLOOKUP(J27,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I27,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="78">
+        <f>IFERROR(VLOOKUP(K27,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M27" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O27" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P27" s="82"/>
+      <c r="Q27" s="82">
+        <v>0</v>
+      </c>
+      <c r="R27" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="51">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H28" s="82"/>
+      <c r="I28" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K28" s="79">
+        <f>IFERROR(VLOOKUP(J28,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I28,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="78">
+        <f>IFERROR(VLOOKUP(K28,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M28" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O28" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P28" s="82"/>
+      <c r="Q28" s="82">
+        <v>0</v>
+      </c>
+      <c r="R28" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="51">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H29" s="82"/>
+      <c r="I29" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J29" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K29" s="79">
+        <f>IFERROR(VLOOKUP(J29,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I29,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="78">
+        <f>IFERROR(VLOOKUP(K29,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M29" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O29" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P29" s="82"/>
+      <c r="Q29" s="82">
+        <v>0</v>
+      </c>
+      <c r="R29" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="51">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H30" s="82"/>
+      <c r="I30" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J30" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K30" s="79">
+        <f>IFERROR(VLOOKUP(J30,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I30,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="78">
+        <f>IFERROR(VLOOKUP(K30,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M30" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O30" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P30" s="82"/>
+      <c r="Q30" s="82">
+        <v>0</v>
+      </c>
+      <c r="R30" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="51">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H31" s="82"/>
+      <c r="I31" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J31" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K31" s="79">
+        <f>IFERROR(VLOOKUP(J31,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I31,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="78">
+        <f>IFERROR(VLOOKUP(K31,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M31" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O31" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="82">
+        <v>0</v>
+      </c>
+      <c r="R31" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="51">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H32" s="82"/>
+      <c r="I32" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J32" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K32" s="79">
+        <f>IFERROR(VLOOKUP(J32,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I32,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="78">
+        <f>IFERROR(VLOOKUP(K32,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M32" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O32" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="82">
+        <v>0</v>
+      </c>
+      <c r="R32" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B33" s="51">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H33" s="82"/>
+      <c r="I33" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K33" s="79">
+        <f>IFERROR(VLOOKUP(J33,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I33,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="78">
+        <f>IFERROR(VLOOKUP(K33,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M33" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N33" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O33" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P33" s="82"/>
+      <c r="Q33" s="82">
+        <v>0</v>
+      </c>
+      <c r="R33" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B34" s="51">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E34" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H34" s="82"/>
+      <c r="I34" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K34" s="79">
+        <f>IFERROR(VLOOKUP(J34,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I34,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="78">
+        <f>IFERROR(VLOOKUP(K34,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M34" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O34" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P34" s="82"/>
+      <c r="Q34" s="82">
+        <v>0</v>
+      </c>
+      <c r="R34" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B35" s="51">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H35" s="82"/>
+      <c r="I35" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J35" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K35" s="79">
+        <f>IFERROR(VLOOKUP(J35,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I35,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="78">
+        <f>IFERROR(VLOOKUP(K35,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M35" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O35" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P35" s="82"/>
+      <c r="Q35" s="82">
+        <v>0</v>
+      </c>
+      <c r="R35" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B36" s="51">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H36" s="82"/>
+      <c r="I36" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J36" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K36" s="79">
+        <f>IFERROR(VLOOKUP(J36,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I36,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="78">
+        <f>IFERROR(VLOOKUP(K36,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M36" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O36" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P36" s="82"/>
+      <c r="Q36" s="82">
+        <v>0</v>
+      </c>
+      <c r="R36" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B37" s="51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H37" s="82"/>
+      <c r="I37" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J37" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K37" s="79">
+        <f>IFERROR(VLOOKUP(J37,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I37,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L37" s="78">
+        <f>IFERROR(VLOOKUP(K37,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M37" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O37" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P37" s="82"/>
+      <c r="Q37" s="82">
+        <v>0</v>
+      </c>
+      <c r="R37" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B38" s="51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H38" s="82"/>
+      <c r="I38" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J38" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K38" s="79">
+        <f>IFERROR(VLOOKUP(J38,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I38,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f>IFERROR(VLOOKUP(K38,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M38" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N38" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="82">
+        <v>0</v>
+      </c>
+      <c r="R38" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B39" s="51">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H39" s="82"/>
+      <c r="I39" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K39" s="79">
+        <f>IFERROR(VLOOKUP(J39,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I39,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="78">
+        <f>IFERROR(VLOOKUP(K39,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M39" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N39" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O39" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="82">
+        <v>0</v>
+      </c>
+      <c r="R39" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B40" s="51">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H40" s="82"/>
+      <c r="I40" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K40" s="79">
+        <f>IFERROR(VLOOKUP(J40,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I40,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="78">
+        <f>IFERROR(VLOOKUP(K40,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M40" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N40" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O40" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82">
+        <v>0</v>
+      </c>
+      <c r="R40" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B41" s="51">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H41" s="82"/>
+      <c r="I41" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J41" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K41" s="79">
+        <f>IFERROR(VLOOKUP(J41,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I41,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="78">
+        <f>IFERROR(VLOOKUP(K41,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M41" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N41" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O41" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P41" s="82"/>
+      <c r="Q41" s="82">
+        <v>0</v>
+      </c>
+      <c r="R41" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="51">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H42" s="82"/>
+      <c r="I42" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J42" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K42" s="79">
+        <f>IFERROR(VLOOKUP(J42,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I42,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="78">
+        <f>IFERROR(VLOOKUP(K42,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M42" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O42" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P42" s="82"/>
+      <c r="Q42" s="82">
+        <v>0</v>
+      </c>
+      <c r="R42" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="51">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="H43" s="82"/>
+      <c r="I43" s="78">
+        <v>0.35416666666666602</v>
+      </c>
+      <c r="J43" s="78">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="K43" s="79">
+        <f>IFERROR(VLOOKUP(J43,기준!B:C,2,FALSE),"")-IFERROR(VLOOKUP(I43,기준!D:E,2,FALSE),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="78">
+        <f>IFERROR(VLOOKUP(K43,기준!F:G,2,FALSE),"")</f>
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M43" s="83">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N43" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="O43" s="78">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="P43" s="82"/>
+      <c r="Q43" s="82">
+        <v>0</v>
+      </c>
+      <c r="R43" s="46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="G4:M4"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O7:O43" xr:uid="{F8BB5D4A-54AD-4CA4-88F3-ED7FFFEEA735}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DAD7BC-F30B-46B1-A8D5-ED1F4951118E}">
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -9710,18 +17047,18 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="99"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="110"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -9760,7 +17097,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="111" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="12" t="s">
@@ -9782,7 +17119,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="101"/>
+      <c r="B5" s="112"/>
       <c r="C5" s="12" t="s">
         <v>14</v>
       </c>
@@ -9802,7 +17139,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="101"/>
+      <c r="B6" s="112"/>
       <c r="C6" s="12" t="s">
         <v>13</v>
       </c>
@@ -9822,7 +17159,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="101"/>
+      <c r="B7" s="112"/>
       <c r="C7" s="12" t="s">
         <v>12</v>
       </c>
@@ -9842,7 +17179,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="101"/>
+      <c r="B8" s="112"/>
       <c r="C8" s="12" t="s">
         <v>11</v>
       </c>
@@ -9862,7 +17199,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="101"/>
+      <c r="B9" s="112"/>
       <c r="C9" s="12" t="s">
         <v>10</v>
       </c>
@@ -9882,7 +17219,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="101"/>
+      <c r="B10" s="112"/>
       <c r="C10" s="12" t="s">
         <v>9</v>
       </c>
@@ -9902,7 +17239,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="101"/>
+      <c r="B11" s="112"/>
       <c r="C11" s="12" t="s">
         <v>8</v>
       </c>
@@ -9922,7 +17259,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="102"/>
+      <c r="B12" s="113"/>
       <c r="C12" s="12" t="s">
         <v>7</v>
       </c>
@@ -9942,7 +17279,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="114" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -9964,7 +17301,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="103"/>
+      <c r="B14" s="114"/>
       <c r="C14" s="12" t="s">
         <v>4</v>
       </c>
@@ -9984,7 +17321,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="114" t="s">
         <v>3</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -10006,7 +17343,7 @@
     </row>
     <row r="16" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
-      <c r="B16" s="104"/>
+      <c r="B16" s="115"/>
       <c r="C16" s="8" t="s">
         <v>1</v>
       </c>
@@ -10024,7 +17361,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:12" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
